--- a/data_processed/results_XGB_m3_gas_per_capitatenure.xlsx
+++ b/data_processed/results_XGB_m3_gas_per_capitatenure.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.8549" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.8568" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27.90624618530273</v>
+        <v>25.66501426696777</v>
       </c>
       <c r="D2" t="n">
-        <v>5.453322887420654</v>
+        <v>5.078277111053467</v>
       </c>
     </row>
     <row r="3">
@@ -467,14 +467,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>building_type</t>
+          <t>household_size</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>97.85591125488281</v>
+        <v>116.3778076171875</v>
       </c>
       <c r="D3" t="n">
-        <v>19.12259674072266</v>
+        <v>23.02740859985352</v>
       </c>
     </row>
     <row r="4">
@@ -483,14 +483,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>building_age</t>
+          <t>dwelling_size</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>76.17104339599609</v>
+        <v>89.26949310302734</v>
       </c>
       <c r="D4" t="n">
-        <v>14.88503074645996</v>
+        <v>17.66354751586914</v>
       </c>
     </row>
     <row r="5">
@@ -499,14 +499,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>population_density</t>
+          <t>building_type</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4.359499931335449</v>
+        <v>93.1063232421875</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8519154191017151</v>
+        <v>18.42273330688477</v>
       </c>
     </row>
     <row r="6">
@@ -515,14 +515,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>household_size</t>
+          <t>building_age</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>117.101936340332</v>
+        <v>74.84736633300781</v>
       </c>
       <c r="D6" t="n">
-        <v>22.88357543945312</v>
+        <v>14.80987548828125</v>
       </c>
     </row>
     <row r="7">
@@ -531,14 +531,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>dwelling_size</t>
+          <t>population_density</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>84.34963989257812</v>
+        <v>3.268163919448853</v>
       </c>
       <c r="D7" t="n">
-        <v>16.48325729370117</v>
+        <v>0.646664023399353</v>
       </c>
     </row>
     <row r="8">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>36.07881164550781</v>
+        <v>35.96128082275391</v>
       </c>
       <c r="D8" t="n">
-        <v>7.050372123718262</v>
+        <v>7.115575313568115</v>
       </c>
     </row>
     <row r="9">
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>67.90608215332031</v>
+        <v>66.892822265625</v>
       </c>
       <c r="D9" t="n">
-        <v>13.26992607116699</v>
+        <v>13.23592758178711</v>
       </c>
     </row>
   </sheetData>
